--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7F05EC-98C3-4316-914E-CE89AA737810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710A8363-649E-4B89-B3C4-80903EB64ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,15 @@
   <si>
     <t>I feel like I have to work on myself in many areas.</t>
   </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>My stomach hurt today after lunch.</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
 </sst>
 </file>
 
@@ -349,7 +358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -393,6 +402,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -870,8 +880,9 @@
     <col min="5" max="5" width="18.6640625" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" customWidth="1"/>
+    <col min="10" max="10" width="23.5546875" customWidth="1"/>
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
@@ -925,8 +936,10 @@
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
+      <c r="F3" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -1082,27 +1095,51 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13">
+        <v>46245</v>
+      </c>
+      <c r="B8" s="14">
+        <v>440</v>
+      </c>
+      <c r="C8" s="14">
+        <v>25</v>
+      </c>
+      <c r="D8" s="14">
+        <v>20</v>
+      </c>
+      <c r="E8" s="14">
+        <v>40</v>
+      </c>
+      <c r="F8" s="14">
+        <v>250</v>
+      </c>
+      <c r="G8" s="14">
+        <v>5</v>
+      </c>
+      <c r="H8" s="14">
+        <v>120</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>895</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>545</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710A8363-649E-4B89-B3C4-80903EB64ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CA0813-FBEC-414E-8F4E-6683C098BB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   <si>
     <t>August</t>
   </si>
+  <si>
+    <t>My right eye is red today and I am tired</t>
+  </si>
 </sst>
 </file>
 
@@ -358,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -402,7 +405,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -936,10 +938,10 @@
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -1141,27 +1143,51 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="13">
+        <v>46246</v>
+      </c>
+      <c r="B9" s="14">
+        <v>440</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <v>400</v>
+      </c>
+      <c r="G9" s="14">
+        <v>8</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24CA0813-FBEC-414E-8F4E-6683C098BB55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE43BF0-AEC7-4584-8ACF-B0E8D3C87CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>My right eye is red today and I am tired</t>
+  </si>
+  <si>
+    <t>I feel good today, I am improving just little bit</t>
   </si>
 </sst>
 </file>
@@ -1189,27 +1192,51 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="13">
+        <v>46247</v>
+      </c>
+      <c r="B10" s="14">
+        <v>430</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>150</v>
+      </c>
+      <c r="E10" s="14">
+        <v>0</v>
+      </c>
+      <c r="F10" s="14">
+        <v>350</v>
+      </c>
+      <c r="G10" s="14">
+        <v>7</v>
+      </c>
+      <c r="H10" s="14">
+        <v>80</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE43BF0-AEC7-4584-8ACF-B0E8D3C87CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89AF3EB-DF7E-4252-A946-3D23C253A091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -225,7 +225,10 @@
     <t>My right eye is red today and I am tired</t>
   </si>
   <si>
-    <t>I feel good today, I am improving just little bit</t>
+    <t>I have a cold today, and my throat hurts.</t>
+  </si>
+  <si>
+    <t>I feel good today, I am improving just little by little</t>
   </si>
 </sst>
 </file>
@@ -1235,30 +1238,54 @@
         <v>51</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="13">
+        <v>46248</v>
+      </c>
+      <c r="B11" s="14">
+        <v>360</v>
+      </c>
+      <c r="C11" s="14">
+        <v>0</v>
+      </c>
+      <c r="D11" s="14">
+        <v>300</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>150</v>
+      </c>
+      <c r="G11" s="14">
+        <v>3</v>
+      </c>
+      <c r="H11" s="14">
+        <v>120</v>
+      </c>
+      <c r="I11" s="15">
+        <f t="shared" si="0"/>
+        <v>930</v>
+      </c>
+      <c r="J11" s="15">
+        <f t="shared" si="1"/>
+        <v>510</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89AF3EB-DF7E-4252-A946-3D23C253A091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D20E339-DD56-4E55-B518-83B13FF56D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,12 @@
   </si>
   <si>
     <t>I feel good today, I am improving just little by little</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Happy independence day, It was good day</t>
   </si>
 </sst>
 </file>
@@ -1287,27 +1293,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="13">
+        <v>46249</v>
+      </c>
+      <c r="B12" s="14">
+        <v>440</v>
+      </c>
+      <c r="C12" s="14">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14">
+        <v>300</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0</v>
+      </c>
+      <c r="G12" s="14">
+        <v>0</v>
+      </c>
+      <c r="H12" s="14">
+        <v>300</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D20E339-DD56-4E55-B518-83B13FF56D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786CA18C-DB7B-4BA7-ADFE-6DEA8CA7F8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>Happy independence day, It was good day</t>
+  </si>
+  <si>
+    <t>Went shopping at DMart today and had a fun time with my friends. It was a nice break and I really enjoyed the day.</t>
   </si>
 </sst>
 </file>
@@ -1339,27 +1342,51 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="13">
+        <v>46250</v>
+      </c>
+      <c r="B13" s="14">
+        <v>440</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>500</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786CA18C-DB7B-4BA7-ADFE-6DEA8CA7F8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462CA2F0-3A3D-4412-80F9-96ED7FAC283E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Went shopping at DMart today and had a fun time with my friends. It was a nice break and I really enjoyed the day.</t>
+  </si>
+  <si>
+    <t>Answered some networking questions today, but a few of my answers were wrong. I also participated in communication skills.</t>
   </si>
 </sst>
 </file>
@@ -1388,27 +1391,51 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="13">
+        <v>46251</v>
+      </c>
+      <c r="B14" s="14">
+        <v>300</v>
+      </c>
+      <c r="C14" s="14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14">
+        <v>60</v>
+      </c>
+      <c r="E14" s="14">
+        <v>0</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>120</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462CA2F0-3A3D-4412-80F9-96ED7FAC283E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93ACE420-3B72-4AC7-A632-FBE8BAD974B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>Answered some networking questions today, but a few of my answers were wrong. I also participated in communication skills.</t>
+  </si>
+  <si>
+    <t>Normal day</t>
   </si>
 </sst>
 </file>
@@ -1438,26 +1441,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="14">
+        <v>440</v>
+      </c>
+      <c r="C15" s="14">
+        <v>0</v>
+      </c>
+      <c r="D15" s="14">
+        <v>160</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>200</v>
+      </c>
+      <c r="G15" s="14">
+        <v>4</v>
+      </c>
+      <c r="H15" s="14">
+        <v>240</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93ACE420-3B72-4AC7-A632-FBE8BAD974B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E461DD-B5C3-43A1-B8E4-EA20DD53E263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,12 @@
   </si>
   <si>
     <t>Normal day</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>I didn't sleep well and I am tired today</t>
   </si>
 </sst>
 </file>
@@ -1448,7 +1454,7 @@
         <v>440</v>
       </c>
       <c r="C15" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D15" s="14">
         <v>160</v>
@@ -1467,11 +1473,11 @@
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>56</v>
@@ -1486,27 +1492,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13">
+        <v>46253</v>
+      </c>
+      <c r="B16" s="14">
+        <v>240</v>
+      </c>
+      <c r="C16" s="14">
+        <v>0</v>
+      </c>
+      <c r="D16" s="14">
+        <v>180</v>
+      </c>
+      <c r="E16" s="14">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>350</v>
+      </c>
+      <c r="G16" s="14">
+        <v>7</v>
+      </c>
+      <c r="H16" s="14">
+        <v>180</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E461DD-B5C3-43A1-B8E4-EA20DD53E263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D22EE7-862D-4E5D-B304-FEB44D842061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1539,26 +1539,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46254</v>
+      </c>
+      <c r="B17" s="14">
+        <v>450</v>
+      </c>
+      <c r="C17" s="14">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>140</v>
+      </c>
+      <c r="E17" s="14">
+        <v>20</v>
+      </c>
+      <c r="F17" s="14">
+        <v>150</v>
+      </c>
+      <c r="G17" s="14">
+        <v>3</v>
+      </c>
+      <c r="H17" s="14">
+        <v>150</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D22EE7-862D-4E5D-B304-FEB44D842061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CC1B91-D451-4D80-AAAB-E7EFD0CF385A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>I didn't sleep well and I am tired today</t>
+  </si>
+  <si>
+    <t>Today I had 5 classes but due to some arragemen issue some teachers were absent</t>
   </si>
 </sst>
 </file>
@@ -1584,27 +1587,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="13">
+        <v>46255</v>
+      </c>
+      <c r="B18" s="14">
+        <v>420</v>
+      </c>
+      <c r="C18" s="14">
+        <v>0</v>
+      </c>
+      <c r="D18" s="14">
+        <v>240</v>
+      </c>
+      <c r="E18" s="14">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
+        <v>150</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="14">
+        <v>150</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CC1B91-D451-4D80-AAAB-E7EFD0CF385A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF7C2FD-A5C9-41B8-8AA0-569E2F967184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Today I had 5 classes but due to some arragemen issue some teachers were absent</t>
+  </si>
+  <si>
+    <t>I went to library for study</t>
   </si>
 </sst>
 </file>
@@ -1634,26 +1637,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46256</v>
+      </c>
+      <c r="B19" s="14">
+        <v>300</v>
+      </c>
+      <c r="C19" s="14">
+        <v>20</v>
+      </c>
+      <c r="D19" s="14">
+        <v>390</v>
+      </c>
+      <c r="E19" s="14">
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>180</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF7C2FD-A5C9-41B8-8AA0-569E2F967184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05CC30A-681D-41A5-9855-EB9B98E2CDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -255,7 +255,10 @@
     <t>Today I had 5 classes but due to some arragemen issue some teachers were absent</t>
   </si>
   <si>
-    <t>I went to library for study</t>
+    <t>I went to library for study for 4 hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I played games today </t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1639,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>46256</v>
       </c>
@@ -1683,26 +1686,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46257</v>
+      </c>
+      <c r="B20" s="14">
+        <v>440</v>
+      </c>
+      <c r="C20" s="14">
+        <v>0</v>
+      </c>
+      <c r="D20" s="14">
+        <v>120</v>
+      </c>
+      <c r="E20" s="14">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>300</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05CC30A-681D-41A5-9855-EB9B98E2CDBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C48C8B9-D920-4BE4-896F-A10191A6A642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t xml:space="preserve">I played games today </t>
+  </si>
+  <si>
+    <t>Our C++ teacher has been changed today and I thin he has deep knowledge about pogramming</t>
   </si>
 </sst>
 </file>
@@ -924,7 +927,7 @@
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="14" max="14" width="56.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1731,27 +1734,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+    <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
+        <v>46258</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>0</v>
+      </c>
+      <c r="D21" s="14">
+        <v>240</v>
+      </c>
+      <c r="E21" s="14">
+        <v>20</v>
+      </c>
+      <c r="F21" s="14">
+        <v>100</v>
+      </c>
+      <c r="G21" s="14">
+        <v>2</v>
+      </c>
+      <c r="H21" s="14">
+        <v>240</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C48C8B9-D920-4BE4-896F-A10191A6A642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501ADB35-BD84-435C-9C95-BCF7CD824ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -261,7 +261,10 @@
     <t xml:space="preserve">I played games today </t>
   </si>
   <si>
-    <t>Our C++ teacher has been changed today and I thin he has deep knowledge about pogramming</t>
+    <t>Our C++ teacher has been changed today and I thik he has deep knowledge about pogramming</t>
+  </si>
+  <si>
+    <t>I didn't sleep well</t>
   </si>
 </sst>
 </file>
@@ -1044,7 +1047,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46223</v>
       </c>
@@ -1090,7 +1093,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>46244</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>46245</v>
       </c>
@@ -1182,7 +1185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>46246</v>
       </c>
@@ -1228,7 +1231,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>46247</v>
       </c>
@@ -1274,7 +1277,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>46248</v>
       </c>
@@ -1320,7 +1323,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>46249</v>
       </c>
@@ -1366,7 +1369,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>46250</v>
       </c>
@@ -1412,7 +1415,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="72" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>46251</v>
       </c>
@@ -1504,7 +1507,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>46253</v>
       </c>
@@ -1596,7 +1599,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>46255</v>
       </c>
@@ -1642,7 +1645,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>46256</v>
       </c>
@@ -1734,7 +1737,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>46258</v>
       </c>
@@ -1781,26 +1784,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B22" s="14">
+        <v>300</v>
+      </c>
+      <c r="C22" s="14">
+        <v>0</v>
+      </c>
+      <c r="D22" s="14">
+        <v>200</v>
+      </c>
+      <c r="E22" s="14">
+        <v>30</v>
+      </c>
+      <c r="F22" s="14">
+        <v>300</v>
+      </c>
+      <c r="G22" s="14">
+        <v>6</v>
+      </c>
+      <c r="H22" s="14">
+        <v>70</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>900</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>540</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{501ADB35-BD84-435C-9C95-BCF7CD824ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B2C32E-3D09-4559-8FEB-F271BD72A1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>I didn't sleep well</t>
+  </si>
+  <si>
+    <t>I’m tired today. It wasn’t a good day, and I didn’t eat lunch. It was also a rainy day.</t>
   </si>
 </sst>
 </file>
@@ -1829,27 +1832,51 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B23" s="14">
+        <v>420</v>
+      </c>
+      <c r="C23" s="14">
+        <v>40</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>400</v>
+      </c>
+      <c r="G23" s="14">
+        <v>8</v>
+      </c>
+      <c r="H23" s="14">
+        <v>60</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>980</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>460</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B2C32E-3D09-4559-8FEB-F271BD72A1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7F7D32-930A-4BC8-86FB-4AB289946095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t>I’m tired today. It wasn’t a good day, and I didn’t eat lunch. It was also a rainy day.</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Today was a good day</t>
   </si>
 </sst>
 </file>
@@ -1879,26 +1885,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B24" s="14">
+        <v>360</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>300</v>
+      </c>
+      <c r="E24" s="14">
+        <v>60</v>
+      </c>
+      <c r="F24" s="14">
+        <v>300</v>
+      </c>
+      <c r="G24" s="14">
+        <v>5</v>
+      </c>
+      <c r="H24" s="14">
+        <v>60</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7F7D32-930A-4BC8-86FB-4AB289946095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63052BAF-7CB4-48CE-9A7B-CA4FBD402A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1931,26 +1931,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46262</v>
+      </c>
+      <c r="B25" s="14">
+        <v>360</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
+      <c r="D25" s="14">
+        <v>0</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>240</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>240</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>Today was a good day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I went to zoodio and D-Mart with my new friends, It was fun </t>
   </si>
 </sst>
 </file>
@@ -734,186 +737,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="105" customWidth="1"/>
+    <col min="1" max="1" width="105.0625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:1" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -925,24 +928,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" customWidth="1"/>
-    <col min="2" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" customWidth="1"/>
-    <col min="10" max="10" width="23.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="56.44140625" customWidth="1"/>
+    <col min="1" max="1" width="36.72265625" customWidth="1"/>
+    <col min="2" max="3" width="11.02734375" customWidth="1"/>
+    <col min="4" max="4" width="13.71875" customWidth="1"/>
+    <col min="5" max="5" width="18.6953125" customWidth="1"/>
+    <col min="6" max="6" width="11.02734375" customWidth="1"/>
+    <col min="7" max="7" width="13.046875" customWidth="1"/>
+    <col min="8" max="8" width="13.98828125" customWidth="1"/>
+    <col min="9" max="9" width="21.38671875" customWidth="1"/>
+    <col min="10" max="10" width="23.5390625" customWidth="1"/>
+    <col min="11" max="11" width="13.046875" customWidth="1"/>
+    <col min="12" max="12" width="14.9296875" customWidth="1"/>
+    <col min="13" max="13" width="11.97265625" customWidth="1"/>
+    <col min="14" max="14" width="56.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
@@ -960,7 +963,7 @@
       <c r="M1" s="19"/>
       <c r="N1" s="19"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -977,7 +980,7 @@
       </c>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -994,7 +997,7 @@
       </c>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
@@ -1012,7 +1015,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="39.75" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="27" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>46223</v>
       </c>
@@ -1102,7 +1105,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="13">
         <v>46244</v>
       </c>
@@ -1148,7 +1151,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
         <v>46245</v>
       </c>
@@ -1194,7 +1197,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
         <v>46246</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
         <v>46247</v>
       </c>
@@ -1286,7 +1289,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
         <v>46248</v>
       </c>
@@ -1332,7 +1335,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
         <v>46249</v>
       </c>
@@ -1378,7 +1381,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
         <v>46250</v>
       </c>
@@ -1424,7 +1427,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A14" s="13">
         <v>46251</v>
       </c>
@@ -1470,7 +1473,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="13">
         <v>46252</v>
       </c>
@@ -1516,7 +1519,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="13">
         <v>46253</v>
       </c>
@@ -1562,7 +1565,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="13">
         <v>46254</v>
       </c>
@@ -1608,7 +1611,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
         <v>46255</v>
       </c>
@@ -1654,7 +1657,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
         <v>46256</v>
       </c>
@@ -1700,7 +1703,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="13">
         <v>46257</v>
       </c>
@@ -1746,7 +1749,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A21" s="13">
         <v>46258</v>
       </c>
@@ -1792,7 +1795,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="13">
         <v>46259</v>
       </c>
@@ -1838,7 +1841,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A23" s="13">
         <v>46260</v>
       </c>
@@ -1884,7 +1887,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="13">
         <v>46261</v>
       </c>
@@ -1930,7 +1933,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="13">
         <v>46262</v>
       </c>
@@ -1976,29 +1979,53 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>0</v>
+      </c>
+      <c r="D26" s="14">
+        <v>120</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>50</v>
+      </c>
+      <c r="G26" s="14">
+        <v>1</v>
+      </c>
+      <c r="H26" s="14">
+        <v>300</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+        <v>550</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -2020,7 +2047,7 @@
       <c r="M27" s="16"/>
       <c r="N27" s="17"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -2042,7 +2069,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -2064,7 +2091,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -2086,7 +2113,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -2108,7 +2135,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -2130,7 +2157,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -2152,7 +2179,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -2174,7 +2201,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -2196,7 +2223,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -2218,7 +2245,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -2240,7 +2267,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -2262,7 +2289,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -2284,7 +2311,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -2306,7 +2333,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -2328,7 +2355,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -2350,7 +2377,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -2372,7 +2399,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -2394,7 +2421,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2416,7 +2443,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2438,7 +2465,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2460,7 +2487,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2482,7 +2509,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2504,7 +2531,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2526,7 +2553,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2548,7 +2575,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2570,7 +2597,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2592,7 +2619,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2614,7 +2641,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2636,7 +2663,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2658,7 +2685,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2680,7 +2707,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2702,7 +2729,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2724,7 +2751,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -2746,7 +2773,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -2768,7 +2795,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -2790,7 +2817,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -2812,7 +2839,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2834,7 +2861,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2856,7 +2883,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2878,7 +2905,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -2900,7 +2927,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2922,7 +2949,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -2944,7 +2971,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -2966,7 +2993,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -2988,7 +3015,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -3010,7 +3037,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -3032,7 +3059,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3054,7 +3081,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -3076,7 +3103,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -3098,7 +3125,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -3120,7 +3147,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -3142,7 +3169,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -3164,7 +3191,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -3186,7 +3213,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -3208,7 +3235,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -3230,7 +3257,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -3252,7 +3279,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -3274,7 +3301,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -3296,7 +3323,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -3318,7 +3345,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -3340,7 +3367,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -3362,7 +3389,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -3384,7 +3411,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -3406,7 +3433,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -3428,7 +3455,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3450,7 +3477,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -3472,7 +3499,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -3494,7 +3521,7 @@
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -3516,7 +3543,7 @@
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -3538,7 +3565,7 @@
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3560,7 +3587,7 @@
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3582,7 +3609,7 @@
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -3604,7 +3631,7 @@
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -3626,7 +3653,7 @@
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -3648,7 +3675,7 @@
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -3670,7 +3697,7 @@
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -3692,7 +3719,7 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -3714,7 +3741,7 @@
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -3736,7 +3763,7 @@
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -3758,7 +3785,7 @@
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -3780,7 +3807,7 @@
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -3802,7 +3829,7 @@
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -3824,7 +3851,7 @@
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -3846,7 +3873,7 @@
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -3868,7 +3895,7 @@
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -3890,7 +3917,7 @@
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -3912,7 +3939,7 @@
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -3934,7 +3961,7 @@
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -3956,7 +3983,7 @@
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -3978,7 +4005,7 @@
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -4000,7 +4027,7 @@
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -4022,7 +4049,7 @@
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -4044,7 +4071,7 @@
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -4066,7 +4093,7 @@
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -4088,7 +4115,7 @@
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -4110,7 +4137,7 @@
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -4132,7 +4159,7 @@
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -4154,7 +4181,7 @@
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -4176,7 +4203,7 @@
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -4198,7 +4225,7 @@
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -4220,7 +4247,7 @@
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -4242,7 +4269,7 @@
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -4264,7 +4291,7 @@
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -4286,7 +4313,7 @@
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -4308,7 +4335,7 @@
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -4330,7 +4357,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -4352,7 +4379,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -4374,7 +4401,7 @@
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -4396,7 +4423,7 @@
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -4418,7 +4445,7 @@
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -4440,7 +4467,7 @@
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -4462,7 +4489,7 @@
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -4484,7 +4511,7 @@
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -4506,7 +4533,7 @@
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -4528,7 +4555,7 @@
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4550,7 +4577,7 @@
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4572,7 +4599,7 @@
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4594,7 +4621,7 @@
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -4616,7 +4643,7 @@
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -4638,7 +4665,7 @@
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -4660,7 +4687,7 @@
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -4682,7 +4709,7 @@
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -4704,7 +4731,7 @@
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -4726,7 +4753,7 @@
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -4748,7 +4775,7 @@
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -4770,7 +4797,7 @@
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -4792,7 +4819,7 @@
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -4814,7 +4841,7 @@
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -4836,7 +4863,7 @@
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -4858,7 +4885,7 @@
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -4880,7 +4907,7 @@
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -4902,7 +4929,7 @@
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -4924,7 +4951,7 @@
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -4946,7 +4973,7 @@
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -4968,7 +4995,7 @@
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -4990,7 +5017,7 @@
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -5012,7 +5039,7 @@
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -5034,7 +5061,7 @@
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -5056,7 +5083,7 @@
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -5078,7 +5105,7 @@
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -5100,7 +5127,7 @@
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -5122,7 +5149,7 @@
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -5144,7 +5171,7 @@
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -5166,7 +5193,7 @@
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -5188,7 +5215,7 @@
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -5210,7 +5237,7 @@
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -5232,7 +5259,7 @@
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -5254,7 +5281,7 @@
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -5276,7 +5303,7 @@
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -5298,7 +5325,7 @@
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -5320,7 +5347,7 @@
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -5342,7 +5369,7 @@
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -5364,7 +5391,7 @@
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -5386,7 +5413,7 @@
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -5408,7 +5435,7 @@
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -5430,7 +5457,7 @@
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -5452,7 +5479,7 @@
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -5474,7 +5501,7 @@
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -5496,7 +5523,7 @@
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5518,7 +5545,7 @@
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5540,7 +5567,7 @@
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5562,7 +5589,7 @@
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5584,7 +5611,7 @@
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -5606,7 +5633,7 @@
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -5628,7 +5655,7 @@
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -5650,7 +5677,7 @@
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -5672,7 +5699,7 @@
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -5694,7 +5721,7 @@
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -5716,7 +5743,7 @@
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -5738,7 +5765,7 @@
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -5760,7 +5787,7 @@
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -5782,7 +5809,7 @@
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -5804,7 +5831,7 @@
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -5826,7 +5853,7 @@
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -5848,7 +5875,7 @@
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -5870,7 +5897,7 @@
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -5892,7 +5919,7 @@
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -5914,7 +5941,7 @@
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -5936,7 +5963,7 @@
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -5958,7 +5985,7 @@
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -5980,7 +6007,7 @@
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -6002,7 +6029,7 @@
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -6024,7 +6051,7 @@
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -6046,7 +6073,7 @@
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -6068,7 +6095,7 @@
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -6090,7 +6117,7 @@
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -6112,7 +6139,7 @@
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -6134,7 +6161,7 @@
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -6156,7 +6183,7 @@
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -6178,7 +6205,7 @@
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -6200,7 +6227,7 @@
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -6222,7 +6249,7 @@
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -6244,7 +6271,7 @@
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -6266,7 +6293,7 @@
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -6288,7 +6315,7 @@
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -6310,7 +6337,7 @@
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -6332,7 +6359,7 @@
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -6354,7 +6381,7 @@
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -6376,7 +6403,7 @@
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -6398,7 +6425,7 @@
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -6420,7 +6447,7 @@
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -6442,7 +6469,7 @@
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -6464,7 +6491,7 @@
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -6486,7 +6513,7 @@
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -6508,7 +6535,7 @@
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -6530,7 +6557,7 @@
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6552,7 +6579,7 @@
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6574,7 +6601,7 @@
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -6596,7 +6623,7 @@
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6618,7 +6645,7 @@
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -6640,7 +6667,7 @@
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -6662,7 +6689,7 @@
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -6684,7 +6711,7 @@
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -6706,7 +6733,7 @@
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -6728,7 +6755,7 @@
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -6750,7 +6777,7 @@
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -6772,7 +6799,7 @@
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -6794,7 +6821,7 @@
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -6816,7 +6843,7 @@
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -6838,7 +6865,7 @@
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -6860,7 +6887,7 @@
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -6882,7 +6909,7 @@
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -6904,7 +6931,7 @@
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -6926,7 +6953,7 @@
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -6948,7 +6975,7 @@
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -6970,7 +6997,7 @@
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -6992,7 +7019,7 @@
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -7014,7 +7041,7 @@
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -7036,7 +7063,7 @@
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -7058,7 +7085,7 @@
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -7080,7 +7107,7 @@
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -7102,7 +7129,7 @@
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -7124,7 +7151,7 @@
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -7146,7 +7173,7 @@
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -7168,7 +7195,7 @@
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -7190,7 +7217,7 @@
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -7212,7 +7239,7 @@
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -7234,7 +7261,7 @@
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -7256,7 +7283,7 @@
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -7278,7 +7305,7 @@
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -7300,7 +7327,7 @@
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -7322,7 +7349,7 @@
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -7344,7 +7371,7 @@
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -7366,7 +7393,7 @@
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -7388,7 +7415,7 @@
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -7410,7 +7437,7 @@
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -7432,7 +7459,7 @@
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7454,7 +7481,7 @@
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7476,7 +7503,7 @@
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -7498,7 +7525,7 @@
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -7520,7 +7547,7 @@
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7542,7 +7569,7 @@
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7564,7 +7591,7 @@
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7586,7 +7613,7 @@
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -7608,7 +7635,7 @@
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -7630,7 +7657,7 @@
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -7652,7 +7679,7 @@
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -7674,7 +7701,7 @@
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -7696,7 +7723,7 @@
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -7718,7 +7745,7 @@
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -7740,7 +7767,7 @@
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -7762,7 +7789,7 @@
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -7784,7 +7811,7 @@
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -7806,7 +7833,7 @@
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -7828,7 +7855,7 @@
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -7850,7 +7877,7 @@
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -7872,7 +7899,7 @@
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -7894,7 +7921,7 @@
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -7916,7 +7943,7 @@
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -7938,7 +7965,7 @@
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -7960,7 +7987,7 @@
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -7982,7 +8009,7 @@
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -8004,7 +8031,7 @@
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -8026,7 +8053,7 @@
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -8048,7 +8075,7 @@
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -8070,7 +8097,7 @@
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -8092,7 +8119,7 @@
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -8114,7 +8141,7 @@
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -8136,7 +8163,7 @@
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -8158,7 +8185,7 @@
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -8180,7 +8207,7 @@
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -8202,7 +8229,7 @@
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -8224,7 +8251,7 @@
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -8246,7 +8273,7 @@
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -8268,7 +8295,7 @@
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -8290,7 +8317,7 @@
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -8312,7 +8339,7 @@
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -8334,7 +8361,7 @@
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -8356,7 +8383,7 @@
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -8378,7 +8405,7 @@
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -8400,7 +8427,7 @@
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -8422,7 +8449,7 @@
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -8444,7 +8471,7 @@
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -8466,7 +8493,7 @@
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -8488,7 +8515,7 @@
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -8510,7 +8537,7 @@
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -8532,7 +8559,7 @@
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8554,7 +8581,7 @@
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8576,7 +8603,7 @@
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -8598,7 +8625,7 @@
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -8620,7 +8647,7 @@
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -8642,7 +8669,7 @@
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -8664,7 +8691,7 @@
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -8686,7 +8713,7 @@
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -8708,7 +8735,7 @@
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -8730,7 +8757,7 @@
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -8752,7 +8779,7 @@
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -8774,7 +8801,7 @@
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -8796,7 +8823,7 @@
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -8818,7 +8845,7 @@
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -8840,7 +8867,7 @@
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -8862,7 +8889,7 @@
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -8884,7 +8911,7 @@
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -8906,7 +8933,7 @@
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -8928,7 +8955,7 @@
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -8950,7 +8977,7 @@
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -8972,7 +8999,7 @@
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -8994,7 +9021,7 @@
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -9016,7 +9043,7 @@
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -9038,7 +9065,7 @@
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -9060,7 +9087,7 @@
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -9082,7 +9109,7 @@
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -9104,7 +9131,7 @@
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -9126,7 +9153,7 @@
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -9148,7 +9175,7 @@
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -9170,7 +9197,7 @@
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -9192,7 +9219,7 @@
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -9214,7 +9241,7 @@
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -9236,7 +9263,7 @@
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -9258,7 +9285,7 @@
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -9280,7 +9307,7 @@
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -9302,7 +9329,7 @@
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -9324,7 +9351,7 @@
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -9346,7 +9373,7 @@
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -9368,7 +9395,7 @@
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -9390,7 +9417,7 @@
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -9412,7 +9439,7 @@
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -9434,7 +9461,7 @@
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -9456,7 +9483,7 @@
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -9478,7 +9505,7 @@
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -9500,7 +9527,7 @@
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -9522,7 +9549,7 @@
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9544,7 +9571,7 @@
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9566,7 +9593,7 @@
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9588,7 +9615,7 @@
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -9610,7 +9637,7 @@
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -9632,7 +9659,7 @@
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -9654,7 +9681,7 @@
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -9676,7 +9703,7 @@
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -9698,7 +9725,7 @@
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -9720,7 +9747,7 @@
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -9742,7 +9769,7 @@
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -9764,7 +9791,7 @@
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -9786,7 +9813,7 @@
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -9808,7 +9835,7 @@
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -9830,7 +9857,7 @@
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -9852,7 +9879,7 @@
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -9874,7 +9901,7 @@
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -9896,7 +9923,7 @@
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -9918,7 +9945,7 @@
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -9940,7 +9967,7 @@
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -9962,7 +9989,7 @@
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -9984,7 +10011,7 @@
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -10006,7 +10033,7 @@
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -10028,7 +10055,7 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -10050,7 +10077,7 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -10072,7 +10099,7 @@
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -10094,7 +10121,7 @@
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -10116,7 +10143,7 @@
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -10138,7 +10165,7 @@
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -10160,7 +10187,7 @@
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -10182,7 +10209,7 @@
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -10204,7 +10231,7 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -10226,7 +10253,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63052BAF-7CB4-48CE-9A7B-CA4FBD402A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBEEA6D-5709-44F3-AC84-3082EEB768ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -277,6 +277,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today I went to zoodio and D-Mart with my new friends, It was fun </t>
+  </si>
+  <si>
+    <t>Normal day, completed some notes of c++ and dbms</t>
   </si>
 </sst>
 </file>
@@ -737,186 +740,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A39"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="105.0625" customWidth="1"/>
+    <col min="1" max="1" width="105.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="22.8" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
     </row>
   </sheetData>
@@ -928,24 +931,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N401"/>
-  <sheetFormatPr defaultColWidth="8.609375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.72265625" customWidth="1"/>
-    <col min="2" max="3" width="11.02734375" customWidth="1"/>
-    <col min="4" max="4" width="13.71875" customWidth="1"/>
-    <col min="5" max="5" width="18.6953125" customWidth="1"/>
-    <col min="6" max="6" width="11.02734375" customWidth="1"/>
-    <col min="7" max="7" width="13.046875" customWidth="1"/>
-    <col min="8" max="8" width="13.98828125" customWidth="1"/>
-    <col min="9" max="9" width="21.38671875" customWidth="1"/>
-    <col min="10" max="10" width="23.5390625" customWidth="1"/>
-    <col min="11" max="11" width="13.046875" customWidth="1"/>
-    <col min="12" max="12" width="14.9296875" customWidth="1"/>
-    <col min="13" max="13" width="11.97265625" customWidth="1"/>
-    <col min="14" max="14" width="56.5" customWidth="1"/>
+    <col min="1" max="1" width="36.6640625" customWidth="1"/>
+    <col min="2" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="23.5546875" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="14.88671875" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="56.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
@@ -963,7 +966,7 @@
       <c r="M1" s="19"/>
       <c r="N1" s="19"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -980,7 +983,7 @@
       </c>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -997,7 +1000,7 @@
       </c>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
@@ -1015,7 +1018,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="1:14" ht="39.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1059,7 +1062,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>46223</v>
       </c>
@@ -1105,7 +1108,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="13">
         <v>46244</v>
       </c>
@@ -1151,7 +1154,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>46245</v>
       </c>
@@ -1197,7 +1200,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="13">
         <v>46246</v>
       </c>
@@ -1243,7 +1246,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>46247</v>
       </c>
@@ -1289,7 +1292,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>46248</v>
       </c>
@@ -1335,7 +1338,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>46249</v>
       </c>
@@ -1381,7 +1384,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="13">
         <v>46250</v>
       </c>
@@ -1427,7 +1430,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>46251</v>
       </c>
@@ -1473,7 +1476,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="13">
         <v>46252</v>
       </c>
@@ -1519,7 +1522,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>46253</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="13">
         <v>46254</v>
       </c>
@@ -1611,7 +1614,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>46255</v>
       </c>
@@ -1657,7 +1660,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="13">
         <v>46256</v>
       </c>
@@ -1703,7 +1706,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>46257</v>
       </c>
@@ -1749,7 +1752,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="13">
         <v>46258</v>
       </c>
@@ -1795,7 +1798,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="13">
         <v>46259</v>
       </c>
@@ -1841,7 +1844,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="27.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="13">
         <v>46260</v>
       </c>
@@ -1887,7 +1890,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="13">
         <v>46261</v>
       </c>
@@ -1933,7 +1936,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="13">
         <v>46262</v>
       </c>
@@ -1979,7 +1982,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="13">
         <v>46263</v>
       </c>
@@ -2025,29 +2028,53 @@
         <v>79</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B27" s="14">
+        <v>420</v>
+      </c>
+      <c r="C27" s="14">
+        <v>0</v>
+      </c>
+      <c r="D27" s="14">
+        <v>300</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14">
+        <v>0</v>
+      </c>
+      <c r="H27" s="14">
+        <v>120</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>870</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+        <v>570</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -2069,7 +2096,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -2091,7 +2118,7 @@
       <c r="M29" s="16"/>
       <c r="N29" s="17"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -2113,7 +2140,7 @@
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -2135,7 +2162,7 @@
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -2157,7 +2184,7 @@
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -2179,7 +2206,7 @@
       <c r="M33" s="16"/>
       <c r="N33" s="17"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -2201,7 +2228,7 @@
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -2223,7 +2250,7 @@
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -2245,7 +2272,7 @@
       <c r="M36" s="16"/>
       <c r="N36" s="17"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -2267,7 +2294,7 @@
       <c r="M37" s="16"/>
       <c r="N37" s="17"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -2289,7 +2316,7 @@
       <c r="M38" s="16"/>
       <c r="N38" s="17"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -2311,7 +2338,7 @@
       <c r="M39" s="16"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -2333,7 +2360,7 @@
       <c r="M40" s="16"/>
       <c r="N40" s="17"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -2355,7 +2382,7 @@
       <c r="M41" s="16"/>
       <c r="N41" s="17"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -2377,7 +2404,7 @@
       <c r="M42" s="16"/>
       <c r="N42" s="17"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -2399,7 +2426,7 @@
       <c r="M43" s="16"/>
       <c r="N43" s="17"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -2421,7 +2448,7 @@
       <c r="M44" s="16"/>
       <c r="N44" s="17"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2443,7 +2470,7 @@
       <c r="M45" s="16"/>
       <c r="N45" s="17"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2465,7 +2492,7 @@
       <c r="M46" s="16"/>
       <c r="N46" s="17"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2487,7 +2514,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2509,7 +2536,7 @@
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2531,7 +2558,7 @@
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2553,7 +2580,7 @@
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2575,7 +2602,7 @@
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2597,7 +2624,7 @@
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2619,7 +2646,7 @@
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2641,7 +2668,7 @@
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2663,7 +2690,7 @@
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2685,7 +2712,7 @@
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2707,7 +2734,7 @@
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2729,7 +2756,7 @@
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2751,7 +2778,7 @@
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -2773,7 +2800,7 @@
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -2795,7 +2822,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -2817,7 +2844,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -2839,7 +2866,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2861,7 +2888,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2883,7 +2910,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2905,7 +2932,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -2927,7 +2954,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2949,7 +2976,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -2971,7 +2998,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -2993,7 +3020,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -3015,7 +3042,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -3037,7 +3064,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -3059,7 +3086,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -3081,7 +3108,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -3103,7 +3130,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -3125,7 +3152,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -3147,7 +3174,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -3169,7 +3196,7 @@
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -3191,7 +3218,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -3213,7 +3240,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -3235,7 +3262,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -3257,7 +3284,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -3279,7 +3306,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -3301,7 +3328,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -3323,7 +3350,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -3345,7 +3372,7 @@
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -3367,7 +3394,7 @@
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -3389,7 +3416,7 @@
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -3411,7 +3438,7 @@
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -3433,7 +3460,7 @@
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -3455,7 +3482,7 @@
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3477,7 +3504,7 @@
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -3499,7 +3526,7 @@
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -3521,7 +3548,7 @@
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -3543,7 +3570,7 @@
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -3565,7 +3592,7 @@
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3587,7 +3614,7 @@
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3609,7 +3636,7 @@
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -3631,7 +3658,7 @@
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -3653,7 +3680,7 @@
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -3675,7 +3702,7 @@
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -3697,7 +3724,7 @@
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -3719,7 +3746,7 @@
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -3741,7 +3768,7 @@
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -3763,7 +3790,7 @@
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -3785,7 +3812,7 @@
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -3807,7 +3834,7 @@
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -3829,7 +3856,7 @@
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -3851,7 +3878,7 @@
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -3873,7 +3900,7 @@
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -3895,7 +3922,7 @@
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -3917,7 +3944,7 @@
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -3939,7 +3966,7 @@
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -3961,7 +3988,7 @@
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -3983,7 +4010,7 @@
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -4005,7 +4032,7 @@
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -4027,7 +4054,7 @@
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -4049,7 +4076,7 @@
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -4071,7 +4098,7 @@
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -4093,7 +4120,7 @@
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -4115,7 +4142,7 @@
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -4137,7 +4164,7 @@
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -4159,7 +4186,7 @@
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -4181,7 +4208,7 @@
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -4203,7 +4230,7 @@
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -4225,7 +4252,7 @@
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -4247,7 +4274,7 @@
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -4269,7 +4296,7 @@
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -4291,7 +4318,7 @@
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -4313,7 +4340,7 @@
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -4335,7 +4362,7 @@
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -4357,7 +4384,7 @@
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -4379,7 +4406,7 @@
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -4401,7 +4428,7 @@
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -4423,7 +4450,7 @@
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -4445,7 +4472,7 @@
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -4467,7 +4494,7 @@
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -4489,7 +4516,7 @@
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -4511,7 +4538,7 @@
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -4533,7 +4560,7 @@
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -4555,7 +4582,7 @@
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4577,7 +4604,7 @@
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4599,7 +4626,7 @@
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4621,7 +4648,7 @@
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -4643,7 +4670,7 @@
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -4665,7 +4692,7 @@
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -4687,7 +4714,7 @@
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -4709,7 +4736,7 @@
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -4731,7 +4758,7 @@
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -4753,7 +4780,7 @@
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -4775,7 +4802,7 @@
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -4797,7 +4824,7 @@
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -4819,7 +4846,7 @@
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -4841,7 +4868,7 @@
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -4863,7 +4890,7 @@
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -4885,7 +4912,7 @@
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -4907,7 +4934,7 @@
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -4929,7 +4956,7 @@
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -4951,7 +4978,7 @@
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -4973,7 +5000,7 @@
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -4995,7 +5022,7 @@
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -5017,7 +5044,7 @@
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -5039,7 +5066,7 @@
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -5061,7 +5088,7 @@
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -5083,7 +5110,7 @@
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -5105,7 +5132,7 @@
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -5127,7 +5154,7 @@
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -5149,7 +5176,7 @@
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -5171,7 +5198,7 @@
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -5193,7 +5220,7 @@
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -5215,7 +5242,7 @@
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -5237,7 +5264,7 @@
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -5259,7 +5286,7 @@
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -5281,7 +5308,7 @@
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -5303,7 +5330,7 @@
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -5325,7 +5352,7 @@
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -5347,7 +5374,7 @@
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -5369,7 +5396,7 @@
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -5391,7 +5418,7 @@
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -5413,7 +5440,7 @@
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -5435,7 +5462,7 @@
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -5457,7 +5484,7 @@
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -5479,7 +5506,7 @@
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -5501,7 +5528,7 @@
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -5523,7 +5550,7 @@
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5545,7 +5572,7 @@
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5567,7 +5594,7 @@
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5589,7 +5616,7 @@
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5611,7 +5638,7 @@
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -5633,7 +5660,7 @@
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -5655,7 +5682,7 @@
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -5677,7 +5704,7 @@
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -5699,7 +5726,7 @@
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -5721,7 +5748,7 @@
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -5743,7 +5770,7 @@
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -5765,7 +5792,7 @@
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -5787,7 +5814,7 @@
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -5809,7 +5836,7 @@
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -5831,7 +5858,7 @@
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -5853,7 +5880,7 @@
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -5875,7 +5902,7 @@
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -5897,7 +5924,7 @@
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -5919,7 +5946,7 @@
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -5941,7 +5968,7 @@
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -5963,7 +5990,7 @@
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -5985,7 +6012,7 @@
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -6007,7 +6034,7 @@
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -6029,7 +6056,7 @@
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -6051,7 +6078,7 @@
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -6073,7 +6100,7 @@
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -6095,7 +6122,7 @@
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -6117,7 +6144,7 @@
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -6139,7 +6166,7 @@
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -6161,7 +6188,7 @@
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -6183,7 +6210,7 @@
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -6205,7 +6232,7 @@
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -6227,7 +6254,7 @@
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -6249,7 +6276,7 @@
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -6271,7 +6298,7 @@
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -6293,7 +6320,7 @@
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -6315,7 +6342,7 @@
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -6337,7 +6364,7 @@
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -6359,7 +6386,7 @@
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -6381,7 +6408,7 @@
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -6403,7 +6430,7 @@
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -6425,7 +6452,7 @@
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -6447,7 +6474,7 @@
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -6469,7 +6496,7 @@
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -6491,7 +6518,7 @@
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -6513,7 +6540,7 @@
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -6535,7 +6562,7 @@
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -6557,7 +6584,7 @@
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6579,7 +6606,7 @@
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6601,7 +6628,7 @@
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -6623,7 +6650,7 @@
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6645,7 +6672,7 @@
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -6667,7 +6694,7 @@
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -6689,7 +6716,7 @@
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -6711,7 +6738,7 @@
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -6733,7 +6760,7 @@
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -6755,7 +6782,7 @@
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -6777,7 +6804,7 @@
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -6799,7 +6826,7 @@
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -6821,7 +6848,7 @@
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -6843,7 +6870,7 @@
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -6865,7 +6892,7 @@
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -6887,7 +6914,7 @@
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -6909,7 +6936,7 @@
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -6931,7 +6958,7 @@
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -6953,7 +6980,7 @@
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -6975,7 +7002,7 @@
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -6997,7 +7024,7 @@
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -7019,7 +7046,7 @@
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -7041,7 +7068,7 @@
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -7063,7 +7090,7 @@
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -7085,7 +7112,7 @@
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -7107,7 +7134,7 @@
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -7129,7 +7156,7 @@
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -7151,7 +7178,7 @@
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -7173,7 +7200,7 @@
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -7195,7 +7222,7 @@
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -7217,7 +7244,7 @@
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -7239,7 +7266,7 @@
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -7261,7 +7288,7 @@
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -7283,7 +7310,7 @@
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -7305,7 +7332,7 @@
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -7327,7 +7354,7 @@
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -7349,7 +7376,7 @@
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -7371,7 +7398,7 @@
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -7393,7 +7420,7 @@
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -7415,7 +7442,7 @@
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -7437,7 +7464,7 @@
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -7459,7 +7486,7 @@
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7481,7 +7508,7 @@
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7503,7 +7530,7 @@
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -7525,7 +7552,7 @@
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -7547,7 +7574,7 @@
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7569,7 +7596,7 @@
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7591,7 +7618,7 @@
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7613,7 +7640,7 @@
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -7635,7 +7662,7 @@
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -7657,7 +7684,7 @@
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -7679,7 +7706,7 @@
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -7701,7 +7728,7 @@
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -7723,7 +7750,7 @@
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -7745,7 +7772,7 @@
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -7767,7 +7794,7 @@
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -7789,7 +7816,7 @@
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -7811,7 +7838,7 @@
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -7833,7 +7860,7 @@
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -7855,7 +7882,7 @@
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -7877,7 +7904,7 @@
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -7899,7 +7926,7 @@
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -7921,7 +7948,7 @@
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -7943,7 +7970,7 @@
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -7965,7 +7992,7 @@
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -7987,7 +8014,7 @@
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -8009,7 +8036,7 @@
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -8031,7 +8058,7 @@
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -8053,7 +8080,7 @@
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -8075,7 +8102,7 @@
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -8097,7 +8124,7 @@
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -8119,7 +8146,7 @@
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -8141,7 +8168,7 @@
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -8163,7 +8190,7 @@
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -8185,7 +8212,7 @@
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -8207,7 +8234,7 @@
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -8229,7 +8256,7 @@
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -8251,7 +8278,7 @@
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -8273,7 +8300,7 @@
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -8295,7 +8322,7 @@
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -8317,7 +8344,7 @@
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -8339,7 +8366,7 @@
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -8361,7 +8388,7 @@
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -8383,7 +8410,7 @@
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -8405,7 +8432,7 @@
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -8427,7 +8454,7 @@
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -8449,7 +8476,7 @@
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -8471,7 +8498,7 @@
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -8493,7 +8520,7 @@
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -8515,7 +8542,7 @@
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -8537,7 +8564,7 @@
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -8559,7 +8586,7 @@
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8581,7 +8608,7 @@
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8603,7 +8630,7 @@
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -8625,7 +8652,7 @@
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -8647,7 +8674,7 @@
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -8669,7 +8696,7 @@
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -8691,7 +8718,7 @@
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -8713,7 +8740,7 @@
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -8735,7 +8762,7 @@
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -8757,7 +8784,7 @@
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -8779,7 +8806,7 @@
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -8801,7 +8828,7 @@
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -8823,7 +8850,7 @@
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -8845,7 +8872,7 @@
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -8867,7 +8894,7 @@
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -8889,7 +8916,7 @@
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -8911,7 +8938,7 @@
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -8933,7 +8960,7 @@
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -8955,7 +8982,7 @@
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -8977,7 +9004,7 @@
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -8999,7 +9026,7 @@
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -9021,7 +9048,7 @@
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -9043,7 +9070,7 @@
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -9065,7 +9092,7 @@
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -9087,7 +9114,7 @@
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -9109,7 +9136,7 @@
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -9131,7 +9158,7 @@
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -9153,7 +9180,7 @@
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -9175,7 +9202,7 @@
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -9197,7 +9224,7 @@
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -9219,7 +9246,7 @@
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -9241,7 +9268,7 @@
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -9263,7 +9290,7 @@
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -9285,7 +9312,7 @@
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -9307,7 +9334,7 @@
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -9329,7 +9356,7 @@
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -9351,7 +9378,7 @@
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -9373,7 +9400,7 @@
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -9395,7 +9422,7 @@
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -9417,7 +9444,7 @@
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -9439,7 +9466,7 @@
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -9461,7 +9488,7 @@
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -9483,7 +9510,7 @@
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -9505,7 +9532,7 @@
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -9527,7 +9554,7 @@
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -9549,7 +9576,7 @@
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9571,7 +9598,7 @@
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9593,7 +9620,7 @@
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9615,7 +9642,7 @@
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -9637,7 +9664,7 @@
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -9659,7 +9686,7 @@
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -9681,7 +9708,7 @@
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -9703,7 +9730,7 @@
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -9725,7 +9752,7 @@
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -9747,7 +9774,7 @@
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -9769,7 +9796,7 @@
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -9791,7 +9818,7 @@
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -9813,7 +9840,7 @@
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -9835,7 +9862,7 @@
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -9857,7 +9884,7 @@
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -9879,7 +9906,7 @@
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -9901,7 +9928,7 @@
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -9923,7 +9950,7 @@
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -9945,7 +9972,7 @@
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -9967,7 +9994,7 @@
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -9989,7 +10016,7 @@
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -10011,7 +10038,7 @@
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -10033,7 +10060,7 @@
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -10055,7 +10082,7 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -10077,7 +10104,7 @@
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -10099,7 +10126,7 @@
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -10121,7 +10148,7 @@
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -10143,7 +10170,7 @@
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -10165,7 +10192,7 @@
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -10187,7 +10214,7 @@
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -10209,7 +10236,7 @@
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -10231,7 +10258,7 @@
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -10253,7 +10280,7 @@
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBEEA6D-5709-44F3-AC84-3082EEB768ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DBC94B-F5DE-437B-AD66-AB76E2C06139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Normal day, completed some notes of c++ and dbms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I watched a movie </t>
   </si>
 </sst>
 </file>
@@ -2075,26 +2078,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B28" s="14">
+        <v>400</v>
+      </c>
+      <c r="C28" s="14">
+        <v>0</v>
+      </c>
+      <c r="D28" s="14">
+        <v>60</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>100</v>
+      </c>
+      <c r="G28" s="14">
+        <v>2</v>
+      </c>
+      <c r="H28" s="14">
+        <v>300</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72DBC94B-F5DE-437B-AD66-AB76E2C06139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1102B4F6-F8FA-446C-A0EF-F75C712E3D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today I watched a movie </t>
+  </si>
+  <si>
+    <t>Today was a good day, I had fun today</t>
   </si>
 </sst>
 </file>
@@ -2124,26 +2127,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B29" s="14">
+        <v>300</v>
+      </c>
+      <c r="C29" s="14">
+        <v>0</v>
+      </c>
+      <c r="D29" s="14">
+        <v>120</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>300</v>
+      </c>
+      <c r="G29" s="14">
+        <v>6</v>
+      </c>
+      <c r="H29" s="14">
+        <v>60</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1102B4F6-F8FA-446C-A0EF-F75C712E3D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7341FA48-658A-49D5-939D-D6406757ACD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Today was a good day, I had fun today</t>
+  </si>
+  <si>
+    <t>Today was my CA of communication, So much syllabus I have to cover, didn't understand netwroking dhcp cli</t>
   </si>
 </sst>
 </file>
@@ -2172,27 +2175,51 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+    <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B30" s="14">
+        <v>320</v>
+      </c>
+      <c r="C30" s="14">
+        <v>0</v>
+      </c>
+      <c r="D30" s="14">
+        <v>30</v>
+      </c>
+      <c r="E30" s="14">
+        <v>150</v>
+      </c>
+      <c r="F30" s="14">
+        <v>400</v>
+      </c>
+      <c r="G30" s="14">
+        <v>8</v>
+      </c>
+      <c r="H30" s="14">
+        <v>50</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7341FA48-658A-49D5-939D-D6406757ACD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E870CD9-4C9D-4D01-B814-D7908BAF7485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>Today was my CA of communication, So much syllabus I have to cover, didn't understand netwroking dhcp cli</t>
+  </si>
+  <si>
+    <t>Today was good day I revised some topic of networking</t>
   </si>
 </sst>
 </file>
@@ -2222,26 +2225,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B31" s="14">
+        <v>450</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>240</v>
+      </c>
+      <c r="E31" s="14">
+        <v>60</v>
+      </c>
+      <c r="F31" s="14">
+        <v>150</v>
+      </c>
+      <c r="G31" s="14">
+        <v>3</v>
+      </c>
+      <c r="H31" s="14">
+        <v>60</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E870CD9-4C9D-4D01-B814-D7908BAF7485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B342B2E9-4C2F-4EA1-B976-563240386E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>Today was good day I revised some topic of networking</t>
+  </si>
+  <si>
+    <t>I was tired today. I didn't getting proper sleep lately</t>
   </si>
 </sst>
 </file>
@@ -2271,26 +2274,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B32" s="14">
+        <v>360</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>240</v>
+      </c>
+      <c r="E32" s="14">
+        <v>30</v>
+      </c>
+      <c r="F32" s="14">
+        <v>300</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>120</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B342B2E9-4C2F-4EA1-B976-563240386E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9602E64-DA36-4E83-A88E-0B4F17BDC6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>I was tired today. I didn't getting proper sleep lately</t>
+  </si>
+  <si>
+    <t>I feel like I have fever but still completed my cpp and networking notes</t>
   </si>
 </sst>
 </file>
@@ -2319,27 +2322,51 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+    <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B33" s="14">
+        <v>450</v>
+      </c>
+      <c r="C33" s="14">
+        <v>0</v>
+      </c>
+      <c r="D33" s="14">
+        <v>300</v>
+      </c>
+      <c r="E33" s="14">
+        <v>30</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>180</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>960</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>480</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9602E64-DA36-4E83-A88E-0B4F17BDC6E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1EB8D8-2C79-4D83-9417-651A4EA6411E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,15 @@
   </si>
   <si>
     <t>I feel like I have fever but still completed my cpp and networking notes</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>I have had fever today, so I didn't do any study today feels wors today</t>
   </si>
 </sst>
 </file>
@@ -2368,27 +2377,51 @@
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B34" s="14">
+        <v>720</v>
+      </c>
+      <c r="C34" s="14">
+        <v>0</v>
+      </c>
+      <c r="D34" s="14">
+        <v>30</v>
+      </c>
+      <c r="E34" s="14">
+        <v>60</v>
+      </c>
+      <c r="F34" s="14">
+        <v>0</v>
+      </c>
+      <c r="G34" s="14">
+        <v>0</v>
+      </c>
+      <c r="H34" s="14">
+        <v>180</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>990</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>450</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F1EB8D8-2C79-4D83-9417-651A4EA6411E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57813A1C-97A5-4EFF-8D18-712E548430CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -307,6 +307,9 @@
   </si>
   <si>
     <t>I have had fever today, so I didn't do any study today feels wors today</t>
+  </si>
+  <si>
+    <t>I had a fever, but I’m feeling better now. Studied DBMS for CA1 today</t>
   </si>
 </sst>
 </file>
@@ -2423,27 +2426,51 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B35" s="14">
+        <v>600</v>
+      </c>
+      <c r="C35" s="14">
+        <v>0</v>
+      </c>
+      <c r="D35" s="14">
+        <v>60</v>
+      </c>
+      <c r="E35" s="14">
+        <v>180</v>
+      </c>
+      <c r="F35" s="14">
+        <v>100</v>
+      </c>
+      <c r="G35" s="14">
+        <v>2</v>
+      </c>
+      <c r="H35" s="14">
+        <v>180</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>320</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57813A1C-97A5-4EFF-8D18-712E548430CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C30A316-90F9-456F-A483-59DA3203B8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>I had a fever, but I’m feeling better now. Studied DBMS for CA1 today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBMS Practical didn't go well I knew the solutions but I got confused and wasted all the time on Msword </t>
   </si>
 </sst>
 </file>
@@ -2472,27 +2475,51 @@
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+    <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B36" s="14">
+        <v>420</v>
+      </c>
+      <c r="C36" s="14">
+        <v>0</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>0</v>
+      </c>
+      <c r="F36" s="14">
+        <v>300</v>
+      </c>
+      <c r="G36" s="14">
+        <v>5</v>
+      </c>
+      <c r="H36" s="14">
+        <v>150</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C30A316-90F9-456F-A483-59DA3203B8FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4B7595-0B3D-45C3-90C4-A2B847FD65AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t xml:space="preserve">DBMS Practical didn't go well I knew the solutions but I got confused and wasted all the time on Msword </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today we had networking CA I think it go decesnt, I felt distracted and sleepy today </t>
   </si>
 </sst>
 </file>
@@ -2521,27 +2524,51 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B37" s="14">
+        <v>450</v>
+      </c>
+      <c r="C37" s="14">
+        <v>0</v>
+      </c>
+      <c r="D37" s="14">
+        <v>120</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>350</v>
+      </c>
+      <c r="G37" s="14">
+        <v>7</v>
+      </c>
+      <c r="H37" s="14">
+        <v>150</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4B7595-0B3D-45C3-90C4-A2B847FD65AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700526A2-96C1-47E9-8D63-5CEB375607C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today we had networking CA I think it go decesnt, I felt distracted and sleepy today </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresher's party </t>
   </si>
 </sst>
 </file>
@@ -2571,26 +2574,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B38" s="14">
+        <v>450</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>60</v>
+      </c>
+      <c r="E38" s="14">
+        <v>0</v>
+      </c>
+      <c r="F38" s="14">
+        <v>200</v>
+      </c>
+      <c r="G38" s="14">
+        <v>4</v>
+      </c>
+      <c r="H38" s="14">
+        <v>300</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{700526A2-96C1-47E9-8D63-5CEB375607C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6DC5A7-BDFD-4410-9DA8-B264554FE33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fresher's party </t>
+  </si>
+  <si>
+    <t>Communication class was good mam appriciated me</t>
   </si>
 </sst>
 </file>
@@ -2620,26 +2623,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B39" s="14">
+        <v>300</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>0</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>200</v>
+      </c>
+      <c r="G39" s="14">
+        <v>4</v>
+      </c>
+      <c r="H39" s="14">
+        <v>120</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>620</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6DC5A7-BDFD-4410-9DA8-B264554FE33A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D727505-5690-4F83-9538-7FEEF5E42DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>Communication class was good mam appriciated me</t>
+  </si>
+  <si>
+    <t>Today I fixed a laptop It was intersting task</t>
   </si>
 </sst>
 </file>
@@ -2669,26 +2672,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B40" s="14">
+        <v>400</v>
+      </c>
+      <c r="C40" s="14">
+        <v>0</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>0</v>
+      </c>
+      <c r="G40" s="14">
+        <v>0</v>
+      </c>
+      <c r="H40" s="14">
+        <v>200</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>720</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>720</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>
